--- a/data/nzd0020/nzd0020.xlsx
+++ b/data/nzd0020/nzd0020.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E259"/>
+  <dimension ref="A1:E260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5857,6 +5857,27 @@
         <v>349.84</v>
       </c>
       <c r="E259" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>318.05</v>
+      </c>
+      <c r="C260" t="n">
+        <v>339.46</v>
+      </c>
+      <c r="D260" t="n">
+        <v>350.65</v>
+      </c>
+      <c r="E260" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -5873,7 +5894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B266"/>
+  <dimension ref="A1:B267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8536,6 +8557,16 @@
       </c>
       <c r="B266" t="n">
         <v>-0.24</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>-0.92</v>
       </c>
     </row>
   </sheetData>
@@ -8704,28 +8735,28 @@
         <v>0.0351</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9732005418269551</v>
+        <v>0.9244232863319886</v>
       </c>
       <c r="J2" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K2" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03988576771205232</v>
+        <v>0.03608591220538815</v>
       </c>
       <c r="M2" t="n">
-        <v>29.1257176868397</v>
+        <v>29.16219490874036</v>
       </c>
       <c r="N2" t="n">
-        <v>1438.175154953614</v>
+        <v>1448.086546152439</v>
       </c>
       <c r="O2" t="n">
-        <v>37.92327985490724</v>
+        <v>38.05373235508495</v>
       </c>
       <c r="P2" t="n">
-        <v>355.0423465997544</v>
+        <v>355.5014732480845</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8782,28 +8813,28 @@
         <v>0.09470000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05325812286282203</v>
+        <v>-0.06466312729776778</v>
       </c>
       <c r="J3" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K3" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00314577562807683</v>
+        <v>0.004603147779533523</v>
       </c>
       <c r="M3" t="n">
-        <v>6.137437065750634</v>
+        <v>6.161989492369975</v>
       </c>
       <c r="N3" t="n">
-        <v>56.3968336979112</v>
+        <v>57.04767362873722</v>
       </c>
       <c r="O3" t="n">
-        <v>7.509782533330189</v>
+        <v>7.552991038571224</v>
       </c>
       <c r="P3" t="n">
-        <v>355.9951446866426</v>
+        <v>356.1028269618378</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8860,28 +8891,28 @@
         <v>0.078</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1583520877181936</v>
+        <v>-0.1626788101273877</v>
       </c>
       <c r="J4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03013097470313675</v>
+        <v>0.0319607350786556</v>
       </c>
       <c r="M4" t="n">
-        <v>5.43373824883758</v>
+        <v>5.427223615993201</v>
       </c>
       <c r="N4" t="n">
-        <v>50.64383637534875</v>
+        <v>50.57330928571474</v>
       </c>
       <c r="O4" t="n">
-        <v>7.116448297806199</v>
+        <v>7.111491354541235</v>
       </c>
       <c r="P4" t="n">
-        <v>360.6351340043103</v>
+        <v>360.675985484537</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -8919,7 +8950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E259"/>
+  <dimension ref="A1:E260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15887,6 +15918,33 @@
         </is>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>-34.803942945393956,173.16546367390237</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>-34.804641576464576,173.165024799861</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>-34.80535373096099,173.16468320617432</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0020/nzd0020.xlsx
+++ b/data/nzd0020/nzd0020.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E260"/>
+  <dimension ref="A1:E261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5880,6 +5880,27 @@
       <c r="E260" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>321.33</v>
+      </c>
+      <c r="C261" t="n">
+        <v>339.5</v>
+      </c>
+      <c r="D261" t="n">
+        <v>351.63</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B267"/>
+  <dimension ref="A1:B268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8567,6 +8588,16 @@
       </c>
       <c r="B267" t="n">
         <v>-0.92</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -8735,28 +8766,28 @@
         <v>0.0351</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9244232863319886</v>
+        <v>0.8789737989247091</v>
       </c>
       <c r="J2" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K2" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03608591220538815</v>
+        <v>0.03274473458951221</v>
       </c>
       <c r="M2" t="n">
-        <v>29.16219490874036</v>
+        <v>29.18748164099034</v>
       </c>
       <c r="N2" t="n">
-        <v>1448.086546152439</v>
+        <v>1455.9983634655</v>
       </c>
       <c r="O2" t="n">
-        <v>38.05373235508495</v>
+        <v>38.15754661224303</v>
       </c>
       <c r="P2" t="n">
-        <v>355.5014732480845</v>
+        <v>355.9313301520883</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8813,28 +8844,28 @@
         <v>0.09470000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06466312729776778</v>
+        <v>-0.07583436260183544</v>
       </c>
       <c r="J3" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K3" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004603147779533523</v>
+        <v>0.006287391858479152</v>
       </c>
       <c r="M3" t="n">
-        <v>6.161989492369975</v>
+        <v>6.185713386599056</v>
       </c>
       <c r="N3" t="n">
-        <v>57.04767362873722</v>
+        <v>57.66579594144392</v>
       </c>
       <c r="O3" t="n">
-        <v>7.552991038571224</v>
+        <v>7.593799835487101</v>
       </c>
       <c r="P3" t="n">
-        <v>356.1028269618378</v>
+        <v>356.2088042228702</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8891,28 +8922,28 @@
         <v>0.078</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1626788101273877</v>
+        <v>-0.1661789802121243</v>
       </c>
       <c r="J4" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K4" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0319607350786556</v>
+        <v>0.03355589740747145</v>
       </c>
       <c r="M4" t="n">
-        <v>5.427223615993201</v>
+        <v>5.417910071357755</v>
       </c>
       <c r="N4" t="n">
-        <v>50.57330928571474</v>
+        <v>50.46101696251917</v>
       </c>
       <c r="O4" t="n">
-        <v>7.111491354541235</v>
+        <v>7.103591835298475</v>
       </c>
       <c r="P4" t="n">
-        <v>360.675985484537</v>
+        <v>360.7091902670549</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -8950,7 +8981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E260"/>
+  <dimension ref="A1:E261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15945,6 +15976,33 @@
         </is>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>-34.80396251179535,173.165490565752</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>-34.80464178398551,173.16502515755093</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>-34.80535798897611,173.16469259469994</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0020/nzd0020.xlsx
+++ b/data/nzd0020/nzd0020.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E261"/>
+  <dimension ref="A1:E262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5901,6 +5901,27 @@
       <c r="E261" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>321.33</v>
+      </c>
+      <c r="C262" t="n">
+        <v>340.11</v>
+      </c>
+      <c r="D262" t="n">
+        <v>352.28</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B268"/>
+  <dimension ref="A1:B269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8598,6 +8619,16 @@
       </c>
       <c r="B268" t="n">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -8766,28 +8797,28 @@
         <v>0.0351</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8789737989247091</v>
+        <v>0.8342772327124777</v>
       </c>
       <c r="J2" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03274473458951221</v>
+        <v>0.02961009151312277</v>
       </c>
       <c r="M2" t="n">
-        <v>29.18748164099034</v>
+        <v>29.20888795081305</v>
       </c>
       <c r="N2" t="n">
-        <v>1455.9983634655</v>
+        <v>1463.527852070028</v>
       </c>
       <c r="O2" t="n">
-        <v>38.15754661224303</v>
+        <v>38.25608254996881</v>
       </c>
       <c r="P2" t="n">
-        <v>355.9313301520883</v>
+        <v>356.356077437294</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8844,28 +8875,28 @@
         <v>0.09470000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07583436260183544</v>
+        <v>-0.08634445292777468</v>
       </c>
       <c r="J3" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K3" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006287391858479152</v>
+        <v>0.00810778519794364</v>
       </c>
       <c r="M3" t="n">
-        <v>6.185713386599056</v>
+        <v>6.206612966440257</v>
       </c>
       <c r="N3" t="n">
-        <v>57.66579594144392</v>
+        <v>58.18997734881729</v>
       </c>
       <c r="O3" t="n">
-        <v>7.593799835487101</v>
+        <v>7.628235533124111</v>
       </c>
       <c r="P3" t="n">
-        <v>356.2088042228702</v>
+        <v>356.3089798352401</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8922,28 +8953,28 @@
         <v>0.078</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1661789802121243</v>
+        <v>-0.1691140019087213</v>
       </c>
       <c r="J4" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K4" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03355589740747145</v>
+        <v>0.03498793799331035</v>
       </c>
       <c r="M4" t="n">
-        <v>5.417910071357755</v>
+        <v>5.406674595250648</v>
       </c>
       <c r="N4" t="n">
-        <v>50.46101696251917</v>
+        <v>50.32578798249297</v>
       </c>
       <c r="O4" t="n">
-        <v>7.103591835298475</v>
+        <v>7.094067097405618</v>
       </c>
       <c r="P4" t="n">
-        <v>360.7091902670549</v>
+        <v>360.7371650595313</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -8981,7 +9012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E261"/>
+  <dimension ref="A1:E262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16003,6 +16034,33 @@
         </is>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>-34.80396251179535,173.165490565752</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>-34.804644948679375,173.16503061232248</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>-34.805360813169415,173.16469882178376</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
